--- a/models/llmusage.xlsx
+++ b/models/llmusage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ymq/py/llmage/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D9690E7-09D9-074E-8A0A-13F0CD2E9F26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{981A4F1C-9794-1C4F-A128-DCDF7721DAAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="40960" yWindow="12500" windowWidth="33600" windowHeight="18800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="95">
   <si>
     <t>name</t>
   </si>
@@ -335,6 +335,14 @@
   </si>
   <si>
     <t>str</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>evalvalue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>评价值</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -954,8 +962,15 @@
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
+      <c r="A10" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" t="s">
+        <v>25</v>
+      </c>
       <c r="G10" s="9"/>
       <c r="H10" s="8"/>
     </row>

--- a/models/llmusage.xlsx
+++ b/models/llmusage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ymq/py/llmage/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{981A4F1C-9794-1C4F-A128-DCDF7721DAAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E61CC1A-6598-A74C-8789-B8DB20105C57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40960" yWindow="12500" windowWidth="33600" windowHeight="18800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="44140" yWindow="13280" windowWidth="33600" windowHeight="18800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="117">
   <si>
     <t>name</t>
   </si>
@@ -338,12 +338,100 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>evalvalue</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>评价值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>amount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交易金额</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交易成本</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>userorgid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ownerid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>模型机构id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户机构id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>status</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>taskid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>start_timestamp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>finish_timestamp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>responsed_timestamp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>开始时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>响应时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>结束时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>time</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>idx1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>unique:taskid</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>idx2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>index:userid</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -825,7 +913,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="2" width="16.1640625" customWidth="1"/>
@@ -963,16 +1051,136 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="7" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="C10" t="s">
-        <v>25</v>
+        <v>109</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>112</v>
       </c>
       <c r="G10" s="9"/>
       <c r="H10" s="8"/>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11" s="9"/>
+      <c r="H11" s="8"/>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" s="9"/>
+      <c r="H12" s="8"/>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D13">
+        <v>32</v>
+      </c>
+      <c r="G13" s="9"/>
+      <c r="H13" s="8"/>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D14">
+        <v>256</v>
+      </c>
+      <c r="G14" s="9"/>
+      <c r="H14" s="8"/>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="D15">
+        <v>18</v>
+      </c>
+      <c r="E15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="D16">
+        <v>18</v>
+      </c>
+      <c r="E16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D17">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D18">
+        <v>32</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -985,13 +1193,13 @@
           <x14:formula1>
             <xm:f>coding!$B$2:$B$12</xm:f>
           </x14:formula1>
-          <xm:sqref>C45:C340</xm:sqref>
+          <xm:sqref>C49:C344</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0BAB398B-DC18-4142-8BF9-7C2CA57240DD}">
           <x14:formula1>
             <xm:f>coding!$B$2:$B$15</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C44</xm:sqref>
+          <xm:sqref>C2:C48</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1019,8 +1227,26 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="7"/>
-      <c r="C2" s="7"/>
+      <c r="A2" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="B2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="5" spans="1:3">
       <c r="C5" s="5"/>

--- a/models/llmusage.xlsx
+++ b/models/llmusage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ymq/py/llmage/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E61CC1A-6598-A74C-8789-B8DB20105C57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D20C042-92AE-5047-96D6-531FAC4D7AD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="44140" yWindow="13280" windowWidth="33600" windowHeight="18800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-32000" yWindow="0" windowWidth="33600" windowHeight="24800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="116">
   <si>
     <t>name</t>
   </si>
@@ -390,31 +390,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>start_timestamp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>finish_timestamp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>responsed_timestamp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>开始时间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>响应时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>结束时间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>time</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -432,6 +412,22 @@
   <si>
     <t>index:userid</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>responsed_seconds</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>finish_seconds</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>accounting_status</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>记账状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1051,81 +1047,97 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>112</v>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10">
+        <v>18</v>
+      </c>
+      <c r="E10">
+        <v>3</v>
       </c>
       <c r="G10" s="9"/>
       <c r="H10" s="8"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="7" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="C11" t="s">
-        <v>34</v>
+        <v>107</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="D11">
+        <v>18</v>
+      </c>
+      <c r="E11">
+        <v>3</v>
       </c>
       <c r="G11" s="9"/>
       <c r="H11" s="8"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="7" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="C12" t="s">
-        <v>34</v>
+        <v>105</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D12">
+        <v>32</v>
       </c>
       <c r="G12" s="9"/>
       <c r="H12" s="8"/>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>92</v>
       </c>
       <c r="D13">
-        <v>32</v>
+        <v>256</v>
       </c>
       <c r="G13" s="9"/>
       <c r="H13" s="8"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="7" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D14">
-        <v>256</v>
-      </c>
-      <c r="G14" s="9"/>
-      <c r="H14" s="8"/>
+        <v>18</v>
+      </c>
+      <c r="E14">
+        <v>5</v>
+      </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>97</v>
@@ -1139,27 +1151,24 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="7" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D16">
-        <v>18</v>
-      </c>
-      <c r="E16">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>92</v>
@@ -1170,10 +1179,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="7" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>92</v>
@@ -1193,13 +1202,13 @@
           <x14:formula1>
             <xm:f>coding!$B$2:$B$12</xm:f>
           </x14:formula1>
-          <xm:sqref>C49:C344</xm:sqref>
+          <xm:sqref>C48:C343</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0BAB398B-DC18-4142-8BF9-7C2CA57240DD}">
           <x14:formula1>
             <xm:f>coding!$B$2:$B$15</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C48</xm:sqref>
+          <xm:sqref>C2:C47</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1228,24 +1237,24 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="7" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B2" t="s">
         <v>33</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="7" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B3" t="s">
         <v>33</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:3">
